--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שני בן משה - שירים לא שלי</v>
+        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410900&amp;sid=e8f61624910ad71cfefc2731eed11f18</v>
+        <v>https://yosmusic.com/%d7%a7%d7%a8%d7%95%d7%9c%d7%99%d7%a0%d7%94-%d7%95%d7%90%d7%95%d7%a8%d7%99-%d7%91%d7%a8%d7%90%d7%95%d7%a0%d7%a8-%d7%9b%d7%a0%d7%a8%d7%95%d7%aa-%d7%aa%d7%a4%d7%99%d7%9c%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "תפילה” של קרולינה הוא מהסוג שלא מנסה להרשים בכוח אלא לחלחל לאט. זוהי בלדת פופ־גרוב עדינה ואינטימית, שנשענת פחות על דרמה גדולה ויותר על אמת רגשית חשופה. קרולינה נשארת כאן מאוד “היא”: סאונד חם, אנושי, מלא נשימה ונוכחות, עם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שני בן משה - שירים לא שלי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ג'קו אייזנברג ורון נשר – קיווינו</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%a7%d7%95-%d7%90%d7%99%d7%99%d7%96%d7%a0%d7%91%d7%a8%d7%92-%d7%95%d7%a8%d7%95%d7%9f-%d7%a0%d7%a9%d7%a8-%d7%a7%d7%99%d7%95%d7%95%d7%99%d7%a0%d7%95/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>השיר "קיווינו” של ג'קו אייזנברג ורון נשר הוא בלדת רוק טעונה שמצליחה להחזיק בו־זמנית גם כאב אישי וגם אמירה חברתית רחבה יותר. זה שיר שלא מציע פתרון ברור. במקום להכריז “יהיה טוב”, הוא נשאר בתוך חוסר הוודאות, בתוך העייפות של</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>ג'קו אייזנברג ורון נשר – קיווינו</v>
+        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
+        <v>בן ארצי – ישראל</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a7%d7%a8%d7%95%d7%9c%d7%99%d7%a0%d7%94-%d7%95%d7%90%d7%95%d7%a8%d7%99-%d7%91%d7%a8%d7%90%d7%95%d7%a0%d7%a8-%d7%9b%d7%a0%d7%a8%d7%95%d7%aa-%d7%aa%d7%a4%d7%99%d7%9c%d7%94/</v>
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%99%d7%a9%d7%a8%d7%90%d7%9c/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "תפילה” של קרולינה הוא מהסוג שלא מנסה להרשים בכוח אלא לחלחל לאט. זוהי בלדת פופ־גרוב עדינה ואינטימית, שנשענת פחות על דרמה גדולה ויותר על אמת רגשית חשופה. קרולינה נשארת כאן מאוד “היא”: סאונד חם, אנושי, מלא נשימה ונוכחות, עם</v>
+        <v>השיר "ישראל” של בן ארצי בנוי כעל פרדוקס רגשי: אהבה עמוקה למדינה לצד תחושת אכזבה קשה ממנה. זה לא שיר מחאה זועם או מהפכני, אלא שיר של אדם שמרגיש שייך – ולכן גם פגוע. דווקא בגלל הטון הפשוט והישיר שלו,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
+        <v>בן ארצי – ישראל</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן ארצי – ישראל</v>
+        <v>משה לוק - מתי יבוא גואלי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%99%d7%a9%d7%a8%d7%90%d7%9c/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410921&amp;sid=46ded035bf04ed44d864fc936f252157</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-17</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "ישראל” של בן ארצי בנוי כעל פרדוקס רגשי: אהבה עמוקה למדינה לצד תחושת אכזבה קשה ממנה. זה לא שיר מחאה זועם או מהפכני, אלא שיר של אדם שמרגיש שייך – ולכן גם פגוע. דווקא בגלל הטון הפשוט והישיר שלו,</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,810 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן ארצי – ישראל</v>
+        <v>משה לוק - מתי יבוא גואלי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>כפיר עזרן - עיניים עצובות - גרסת היוצר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410920&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>כפיר עזרן - עיניים עצובות - גרסת היוצר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>כפיר עזרן - עיניים עצובות - גרסה מהירה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410919&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>כפיר עזרן - עיניים עצובות - גרסה מהירה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ישראל זאודה - מה בליבו של גבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410918&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ישראל זאודה - מה בליבו של גבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יניב בן ישי - קשה בלב</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410917&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יניב בן ישי - קשה בלב</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אילון אלקיים - הנסיך שלי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410916&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אילון אלקיים - הנסיך שלי</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אייל לוי &amp; סטפן לגר - חצופה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410915&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אייל לוי &amp; סטפן לגר - חצופה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>רז ארגס - טיול של שבת</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410914&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>רז ארגס - טיול של שבת</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>רועי קורנבלום - גבר גבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410913&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>רועי קורנבלום - גבר גבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>רועי בנטין - איפה את</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410912&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>רועי בנטין - איפה את</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>מידד טסה - עליי תשמור</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410911&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>מידד טסה - עליי תשמור</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>מאיה בוסקילה - קח אותי לרקוד</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410910&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>מאיה בוסקילה - קח אותי לרקוד</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>מאור אדרי - פלה מראדונה</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410909&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>מאור אדרי - פלה מראדונה</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>יהונתן פתחיה - המבט שלך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410908&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>יהונתן פתחיה - המבט שלך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>טל ועקנין - פאפאוטה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410907&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>טל ועקנין - פאפאוטה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>טינה איב - סימנים</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410906&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>טינה איב - סימנים</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>הדר זעפרני - הדרך לי בית</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410905&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>הדר זעפרני - הדרך לי בית</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>בן ארצי - ישראל</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410904&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>בן ארצי - ישראל</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>אמנון בן ש''ך - ים התמימות</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410903&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>אמנון בן ש''ך - ים התמימות</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>אלישיב-ציון אביאל - תרקוד</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410902&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>אלישיב-ציון אביאל - תרקוד</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>אורצ'וק הקטן - אוהב כל רגע</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410901&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>אורצ'וק הקטן - אוהב כל רגע</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>מאיה בוסקילה – קח אותי לרקוד</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C23" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99%d7%94-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a7%d7%97-%d7%90%d7%95%d7%aa%d7%99-%d7%9c%d7%a8%d7%a7%d7%95%d7%93/</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>מאיה בוסקילה לוקחת נוסחה מוכרת של פופ־דאנס ים־תיכוני, והופכת אותה להצהרה רגשית על פחד, תשוקה וחופש אישי. זה שיר שנשמע קודם כול כמו להיט מועדונים גדול, אבל מתחת לביט הכבד והדרמה הווקאלית מסתתר סיפור על אנשים שמפחדים לאהוב בגלוי. הקונפליקט</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>מאיה בוסקילה – קח אותי לרקוד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה לוק - מתי יבוא גואלי</v>
+        <v>שמעון שובייב - סיפור בלי התחלה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410921&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410928&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה לוק - מתי יבוא גואלי</v>
+        <v>שמעון שובייב - סיפור בלי התחלה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>כפיר עזרן - עיניים עצובות - גרסת היוצר</v>
+        <v>רזיאל חי - תפילת הילדים</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410920&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410927&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>כפיר עזרן - עיניים עצובות - גרסת היוצר</v>
+        <v>רזיאל חי - תפילת הילדים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>כפיר עזרן - עיניים עצובות - גרסה מהירה</v>
+        <v>עידו כנפי - הלב מושך הביתה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410919&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410926&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>כפיר עזרן - עיניים עצובות - גרסה מהירה</v>
+        <v>עידו כנפי - הלב מושך הביתה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ישראל זאודה - מה בליבו של גבר</v>
+        <v>עומרי גורן - ויהי נעם</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410918&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410925&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ישראל זאודה - מה בליבו של גבר</v>
+        <v>עומרי גורן - ויהי נעם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יניב בן ישי - קשה בלב</v>
+        <v>עדן ג'לח - תורי לזרוח</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410917&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410924&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-17</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יניב בן ישי - קשה בלב</v>
+        <v>עדן ג'לח - תורי לזרוח</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אילון אלקיים - הנסיך שלי</v>
+        <v>נויה אוזן - טיפוטה</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410916&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410923&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-17</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אילון אלקיים - הנסיך שלי</v>
+        <v>נויה אוזן - טיפוטה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אייל לוי &amp; סטפן לגר - חצופה</v>
+        <v>נהוראי אביסרור - שוהם</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410915&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410922&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-17</v>
@@ -697,582 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אייל לוי &amp; סטפן לגר - חצופה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>רז ארגס - טיול של שבת</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410914&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>רז ארגס - טיול של שבת</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>רועי קורנבלום - גבר גבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410913&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>רועי קורנבלום - גבר גבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>רועי בנטין - איפה את</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410912&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>רועי בנטין - איפה את</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>מידד טסה - עליי תשמור</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410911&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>מידד טסה - עליי תשמור</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>מאיה בוסקילה - קח אותי לרקוד</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410910&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>מאיה בוסקילה - קח אותי לרקוד</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>מאור אדרי - פלה מראדונה</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410909&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>מאור אדרי - פלה מראדונה</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>יהונתן פתחיה - המבט שלך</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410908&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>יהונתן פתחיה - המבט שלך</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>טל ועקנין - פאפאוטה</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410907&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>טל ועקנין - פאפאוטה</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>טינה איב - סימנים</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410906&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>טינה איב - סימנים</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>הדר זעפרני - הדרך לי בית</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410905&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v>הדר זעפרני - הדרך לי בית</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>בן ארצי - ישראל</v>
-      </c>
-      <c r="B19" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410904&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D19" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v>בן ארצי - ישראל</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>אמנון בן ש''ך - ים התמימות</v>
-      </c>
-      <c r="B20" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410903&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D20" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v>אמנון בן ש''ך - ים התמימות</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>אלישיב-ציון אביאל - תרקוד</v>
-      </c>
-      <c r="B21" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410902&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D21" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v>אלישיב-ציון אביאל - תרקוד</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>אורצ'וק הקטן - אוהב כל רגע</v>
-      </c>
-      <c r="B22" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410901&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D22" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v>אורצ'וק הקטן - אוהב כל רגע</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>מאיה בוסקילה – קח אותי לרקוד</v>
-      </c>
-      <c r="B23" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C23" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99%d7%94-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a7%d7%97-%d7%90%d7%95%d7%aa%d7%99-%d7%9c%d7%a8%d7%a7%d7%95%d7%93/</v>
-      </c>
-      <c r="D23" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v>מאיה בוסקילה לוקחת נוסחה מוכרת של פופ־דאנס ים־תיכוני, והופכת אותה להצהרה רגשית על פחד, תשוקה וחופש אישי. זה שיר שנשמע קודם כול כמו להיט מועדונים גדול, אבל מתחת לביט הכבד והדרמה הווקאלית מסתתר סיפור על אנשים שמפחדים לאהוב בגלוי. הקונפליקט</v>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v>מאיה בוסקילה – קח אותי לרקוד</v>
+        <v>נהוראי אביסרור - שוהם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון שובייב - סיפור בלי התחלה</v>
+        <v>מני חן - אחת ממליון</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410928&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410938&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון שובייב - סיפור בלי התחלה</v>
+        <v>מני חן - אחת ממליון</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רזיאל חי - תפילת הילדים</v>
+        <v>נתנאל קהניאל מארח את קלייב ג׳ין - אורך ימים</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410927&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410937&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רזיאל חי - תפילת הילדים</v>
+        <v>נתנאל קהניאל מארח את קלייב ג׳ין - אורך ימים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עידו כנפי - הלב מושך הביתה</v>
+        <v>נוימן - דדליין</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410926&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410936&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עידו כנפי - הלב מושך הביתה</v>
+        <v>נוימן - דדליין</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עומרי גורן - ויהי נעם</v>
+        <v>נאוריאל דרהם - בני יהודה החלום הכתום 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410925&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410935&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עומרי גורן - ויהי נעם</v>
+        <v>נאוריאל דרהם - בני יהודה החלום הכתום 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עדן ג'לח - תורי לזרוח</v>
+        <v>רונה גולד - לטובה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410924&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410934&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-17</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עדן ג'לח - תורי לזרוח</v>
+        <v>רונה גולד - לטובה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נויה אוזן - טיפוטה</v>
+        <v>דולב הרץ - לחזור</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410923&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410933&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-17</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>נויה אוזן - טיפוטה</v>
+        <v>דולב הרץ - לחזור</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נהוראי אביסרור - שוהם</v>
+        <v>דולב הרץ - גיבור</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410922&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410932&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-17</v>
@@ -697,12 +697,126 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>נהוראי אביסרור - שוהם</v>
+        <v>דולב הרץ - גיבור</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דולב הרץ - בן אדם</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410931&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דולב הרץ - בן אדם</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלי הרצליך - מחרוזת סיום הש''ס 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410930&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלי הרצליך - מחרוזת סיום הש''ס 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אוריאל גבאי - מתיקות התורה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410929&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אוריאל גבאי - מתיקות התורה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מני חן - אחת ממליון</v>
+        <v>מיקה משה ואלי חולי – כמו פעם</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410938&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a7%d7%94-%d7%9e%d7%a9%d7%94-%d7%95%d7%90%d7%9c%d7%99-%d7%97%d7%95%d7%9c%d7%99-%d7%9b%d7%9e%d7%95-%d7%a4%d7%a2%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>מיקה משה ואלי חולי שרים דואט שבנוי כמעט כמו מסע רגשי מדורג – גם מוזיקלית וגם טקסטואלית. הוא מתחיל באינטימיות שקטה, מטפס לכאב מתפרץ, ואז נסחף למיד־טמפו רגשי שמרגיש כמו ניסיון להיאחז בזיכרון לפני שהוא נעלם. הכניסה של אלי חולי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,354 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מני חן - אחת ממליון</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>נתנאל קהניאל מארח את קלייב ג׳ין - אורך ימים</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410937&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>נתנאל קהניאל מארח את קלייב ג׳ין - אורך ימים</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נוימן - דדליין</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410936&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נוימן - דדליין</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נאוריאל דרהם - בני יהודה החלום הכתום 2026</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410935&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נאוריאל דרהם - בני יהודה החלום הכתום 2026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>רונה גולד - לטובה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410934&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>רונה גולד - לטובה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>דולב הרץ - לחזור</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410933&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>דולב הרץ - לחזור</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>דולב הרץ - גיבור</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410932&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>דולב הרץ - גיבור</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>דולב הרץ - בן אדם</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410931&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>דולב הרץ - בן אדם</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אלי הרצליך - מחרוזת סיום הש''ס 2026</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410930&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אלי הרצליך - מחרוזת סיום הש''ס 2026</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אוריאל גבאי - מתיקות התורה</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410929&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אוריאל גבאי - מתיקות התורה</v>
+        <v>מיקה משה ואלי חולי – כמו פעם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקה משה ואלי חולי – כמו פעם</v>
+        <v>שלומית אהרון – פיסות אהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a7%d7%94-%d7%9e%d7%a9%d7%94-%d7%95%d7%90%d7%9c%d7%99-%d7%97%d7%95%d7%9c%d7%99-%d7%9b%d7%9e%d7%95-%d7%a4%d7%a2%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99%d7%aa-%d7%90%d7%94%d7%a8%d7%95%d7%9f-%d7%a4%d7%99%d7%a1%d7%95%d7%aa-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מיקה משה ואלי חולי שרים דואט שבנוי כמעט כמו מסע רגשי מדורג – גם מוזיקלית וגם טקסטואלית. הוא מתחיל באינטימיות שקטה, מטפס לכאב מתפרץ, ואז נסחף למיד־טמפו רגשי שמרגיש כמו ניסיון להיאחז בזיכרון לפני שהוא נעלם. הכניסה של אלי חולי</v>
+        <v>שלומית אהרון מגישה ב־"פיסות אהבה" שיר שנשען על מסורת הפופ המלודי הקלאסי של שנות ה־70 וה־80. . זהו שיר שמחבר בין אסתטיקה “אולד סקול” לבין חרדה קיומית,  והחיבור הזה הוא מקור הכוח שלו. צליל האקורדיון בפתיחה מייצר אווירת שנסון אירופי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקה משה ואלי חולי – כמו פעם</v>
+        <v>שלומית אהרון – פיסות אהבה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>תמר גלעדי קרני פוסטל שאול בסר – רוצי מריה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%92%d7%9c%d7%a2%d7%93%d7%99-%d7%a7%d7%a8%d7%a0%d7%99-%d7%a4%d7%95%d7%a1%d7%98%d7%9c-%d7%a9%d7%90%d7%95%d7%9c-%d7%91%d7%a1%d7%a8-%d7%a8%d7%95%d7%a6%d7%99-%d7%9e%d7%a8%d7%99%d7%94/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>השיר “רוצי מריה” כשמבוצע על ידי תמר גלעדי בליווי קרני פוסטל ושאול בסר הוא יצירה שממוקמת על התפר שבין שיר אמנותי (art song) לבין בלדה פופולרית מינורית-קלאסית. זהו ביצוע שמבוסס על לחן של קרלוס אנטוניו ז’ובים (Tom Jobim), כאשר הטקסט</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>תמר גלעדי קרני פוסטל שאול בסר – רוצי מריה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומית אהרון – פיסות אהבה</v>
+        <v>עופרי שגיב - שוב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99%d7%aa-%d7%90%d7%94%d7%a8%d7%95%d7%9f-%d7%a4%d7%99%d7%a1%d7%95%d7%aa-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410945&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שלומית אהרון מגישה ב־"פיסות אהבה" שיר שנשען על מסורת הפופ המלודי הקלאסי של שנות ה־70 וה־80. . זהו שיר שמחבר בין אסתטיקה “אולד סקול” לבין חרדה קיומית,  והחיבור הזה הוא מקור הכוח שלו. צליל האקורדיון בפתיחה מייצר אווירת שנסון אירופי</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומית אהרון – פיסות אהבה</v>
+        <v>עופרי שגיב - שוב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תמר גלעדי קרני פוסטל שאול בסר – רוצי מריה</v>
+        <v>עופר סופר - ירושלים</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%92%d7%9c%d7%a2%d7%93%d7%99-%d7%a7%d7%a8%d7%a0%d7%99-%d7%a4%d7%95%d7%a1%d7%98%d7%9c-%d7%a9%d7%90%d7%95%d7%9c-%d7%91%d7%a1%d7%a8-%d7%a8%d7%95%d7%a6%d7%99-%d7%9e%d7%a8%d7%99%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410944&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-19</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>השיר “רוצי מריה” כשמבוצע על ידי תמר גלעדי בליווי קרני פוסטל ושאול בסר הוא יצירה שממוקמת על התפר שבין שיר אמנותי (art song) לבין בלדה פופולרית מינורית-קלאסית. זהו ביצוע שמבוסס על לחן של קרלוס אנטוניו ז’ובים (Tom Jobim), כאשר הטקסט</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,12 +507,202 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תמר גלעדי קרני פוסטל שאול בסר – רוצי מריה</v>
+        <v>עופר סופר - ירושלים</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ניצן פלד - פחדים</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410943&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>ניצן פלד - פחדים</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מיקה משה &amp; אלי חולי - כמו פעם</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410942&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מיקה משה &amp; אלי חולי - כמו פעם</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מיה סולימן - לב שבור ואלכוהול</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410941&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מיה סולימן - לב שבור ואלכוהול</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>גלילי - אני עשיר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410940&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>גלילי - אני עשיר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אופירה שופן - אין ידידות</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410939&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אופירה שופן - אין ידידות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עופרי שגיב - שוב</v>
+        <v>יניב גליסקו - מחרוזת בית"ר ירושלים 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410945&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410957&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עופרי שגיב - שוב</v>
+        <v>יניב גליסקו - מחרוזת בית"ר ירושלים 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עופר סופר - ירושלים</v>
+        <v>ינון אליה - הילד שהייתי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410944&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410956&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עופר סופר - ירושלים</v>
+        <v>ינון אליה - הילד שהייתי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ניצן פלד - פחדים</v>
+        <v>יוני מאמוש - עשן מהלב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410943&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410955&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ניצן פלד - פחדים</v>
+        <v>יוני מאמוש - עשן מהלב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מיקה משה &amp; אלי חולי - כמו פעם</v>
+        <v>טל גירטלר - חוזרת אלייך</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410942&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410948&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מיקה משה &amp; אלי חולי - כמו פעם</v>
+        <v>טל גירטלר - חוזרת אלייך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מיה סולימן - לב שבור ואלכוהול</v>
+        <v>דורון רוקח - מחרוזת געגועים 2026</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410941&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410947&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-19</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מיה סולימן - לב שבור ואלכוהול</v>
+        <v>דורון רוקח - מחרוזת געגועים 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>גלילי - אני עשיר</v>
+        <v>רון קטן - חיים חדשים</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410940&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410946&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-19</v>
@@ -659,50 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>גלילי - אני עשיר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אופירה שופן - אין ידידות</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410939&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אופירה שופן - אין ידידות</v>
+        <v>רון קטן - חיים חדשים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יניב גליסקו - מחרוזת בית"ר ירושלים 2026</v>
+        <v>יובל גולד ושירה זלוף – מחר יבוא מחר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410957&amp;sid=d5a00c8429477199f3ccba812a262145</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%95%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%9e%d7%97%d7%a8-%d7%99%d7%91%d7%95%d7%90-%d7%9e%d7%97%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "מחר יבוא מחר" של יובל גולד ושירה זלוף מצליח משלב בין פופ עכשווי, רגש חשוף ואווירה ישראלית של חוסר יציבות – גם בזוגיות וגם בחיים עצמם. החיבור בין שני בוגרי הכוכב הבא יוצר דואט שמרגיש טבעי ולא מתאמץ, כמעט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יניב גליסקו - מחרוזת בית"ר ירושלים 2026</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ינון אליה - הילד שהייתי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410956&amp;sid=d5a00c8429477199f3ccba812a262145</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>ינון אליה - הילד שהייתי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>יוני מאמוש - עשן מהלב</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410955&amp;sid=d5a00c8429477199f3ccba812a262145</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>יוני מאמוש - עשן מהלב</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>טל גירטלר - חוזרת אלייך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410948&amp;sid=d5a00c8429477199f3ccba812a262145</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>טל גירטלר - חוזרת אלייך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>דורון רוקח - מחרוזת געגועים 2026</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410947&amp;sid=d5a00c8429477199f3ccba812a262145</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>דורון רוקח - מחרוזת געגועים 2026</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>רון קטן - חיים חדשים</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410946&amp;sid=d5a00c8429477199f3ccba812a262145</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>רון קטן - חיים חדשים</v>
+        <v>יובל גולד ושירה זלוף – מחר יבוא מחר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל גולד ושירה זלוף – מחר יבוא מחר</v>
+        <v>יוני רכטר ואלי דג׳יברי – זו אותה האהבה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%95%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%9e%d7%97%d7%a8-%d7%99%d7%91%d7%95%d7%90-%d7%9e%d7%97%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%95%d7%90%d7%9c%d7%99-%d7%93%d7%92%d7%b3%d7%99%d7%91%d7%a8%d7%99-%d7%96%d7%95-%d7%90%d7%95%d7%aa%d7%94-%d7%94%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-20</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "מחר יבוא מחר" של יובל גולד ושירה זלוף מצליח משלב בין פופ עכשווי, רגש חשוף ואווירה ישראלית של חוסר יציבות – גם בזוגיות וגם בחיים עצמם. החיבור בין שני בוגרי הכוכב הבא יוצר דואט שמרגיש טבעי ולא מתאמץ, כמעט</v>
+        <v>הקאבר החדש של יוני רכטר ואלי דג'יברי ל־"זו אותה האהבה" אינו רק ביצוע מחודש לשירו הקלאסי של אריק איינשטיין  אלא גרסה בוגרת ואינטימית לטקסט שנשמע היום כמעט עמוק יותר משהיה בזמן שנכתב.זהו ביצוע שמוותר על נוסטלגיה "גדולה מהחיים", ובוחר במקום</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל גולד ושירה זלוף – מחר יבוא מחר</v>
+        <v>יוני רכטר ואלי דג׳יברי – זו אותה האהבה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוני רכטר ואלי דג׳יברי – זו אותה האהבה</v>
+        <v>שלומית אהרון - פיסות אהבה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%95%d7%90%d7%9c%d7%99-%d7%93%d7%92%d7%b3%d7%99%d7%91%d7%a8%d7%99-%d7%96%d7%95-%d7%90%d7%95%d7%aa%d7%94-%d7%94%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410969&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-20</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר החדש של יוני רכטר ואלי דג'יברי ל־"זו אותה האהבה" אינו רק ביצוע מחודש לשירו הקלאסי של אריק איינשטיין  אלא גרסה בוגרת ואינטימית לטקסט שנשמע היום כמעט עמוק יותר משהיה בזמן שנכתב.זהו ביצוע שמוותר על נוסטלגיה "גדולה מהחיים", ובוחר במקום</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוני רכטר ואלי דג׳יברי – זו אותה האהבה</v>
+        <v>שלומית אהרון - פיסות אהבה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט - איך שהיא רוקדת</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410968&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט - איך שהיא רוקדת</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עדן בן זקן &amp; נועה קירל - אני משקרת</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410967&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עדן בן זקן &amp; נועה קירל - אני משקרת</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נתנאל ששון - סטלה עבאד</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410966&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נתנאל ששון - סטלה עבאד</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נוריאל חדד - יורד הליל</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410965&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נוריאל חדד - יורד הליל</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>נויה גליק - זמן</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410964&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>נויה גליק - זמן</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אסתר שמיר &amp; יהל דורון - בצד השני של הפחד</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410963&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אסתר שמיר &amp; יהל דורון - בצד השני של הפחד</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>החצר האחורית של ג'וני - טרף קל</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410962&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>החצר האחורית של ג'וני - טרף קל</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אורי כלטוב - לא רוצה לאהוב אותי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410961&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אורי כלטוב - לא רוצה לאהוב אותי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומית אהרון - פיסות אהבה</v>
+        <v>עדן בן זקן &amp; נועה קירל – אני משקרת?</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410969&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%90%d7%a0%d7%99-%d7%9e%d7%a9%d7%a7%d7%a8%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר “אני משקרת?” של נועה קירל ועדן בן זקן מרגיש כמעט כמו ניסוי מעבדה בפופ ישראלי של 2026.  לוקחים שתי מכונות־להיטים עם פרסונות שונות, מערבבים הומור אינטרנטי, אסתטיקת AI, מזרחית־פופ־דאנס, ומוציאים מוצר שנשמע בו־זמנית מודע לעצמו וציני כלפי עצם הרעיון</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומית אהרון - פיסות אהבה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט - איך שהיא רוקדת</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410968&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט - איך שהיא רוקדת</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עדן בן זקן &amp; נועה קירל - אני משקרת</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410967&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עדן בן זקן &amp; נועה קירל - אני משקרת</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נתנאל ששון - סטלה עבאד</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410966&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נתנאל ששון - סטלה עבאד</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נוריאל חדד - יורד הליל</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410965&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נוריאל חדד - יורד הליל</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>נויה גליק - זמן</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410964&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>נויה גליק - זמן</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אסתר שמיר &amp; יהל דורון - בצד השני של הפחד</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410963&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אסתר שמיר &amp; יהל דורון - בצד השני של הפחד</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>החצר האחורית של ג'וני - טרף קל</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410962&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>החצר האחורית של ג'וני - טרף קל</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אורי כלטוב - לא רוצה לאהוב אותי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410961&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אורי כלטוב - לא רוצה לאהוב אותי</v>
+        <v>עדן בן זקן &amp; נועה קירל – אני משקרת?</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן &amp; נועה קירל – אני משקרת?</v>
+        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט – איך שהיא רוקדת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%90%d7%a0%d7%99-%d7%9e%d7%a9%d7%a7%d7%a8%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%9e%d7%90%d7%a8%d7%97%d7%99%d7%9d-%d7%90%d7%aa-%d7%90%d7%92%d7%9d-%d7%91%d7%95%d7%97%d7%91%d7%95/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-21</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “אני משקרת?” של נועה קירל ועדן בן זקן מרגיש כמעט כמו ניסוי מעבדה בפופ ישראלי של 2026.  לוקחים שתי מכונות־להיטים עם פרסונות שונות, מערבבים הומור אינטרנטי, אסתטיקת AI, מזרחית־פופ־דאנס, ומוציאים מוצר שנשמע בו־זמנית מודע לעצמו וציני כלפי עצם הרעיון</v>
+        <v>השיר "איך שהיא רוקדת" של עדן חסון ואופק אדנק יחד עם אגם בוחבוט בנוי כמעט באופן מובהק כ"להיט קיץ" ישראלי עכשווי, כזה שמכוון לפלייליסטים, נסיעות, מסיבות ובריכות. אבל מתחת לקלילות שלו יש כמה שכבות מעניינות מבחינה מוזיקלית והפקתית. כבר מהשורות:</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן בן זקן &amp; נועה קירל – אני משקרת?</v>
+        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט – איך שהיא רוקדת</v>
       </c>
     </row>
   </sheetData>
